--- a/ig/ch-term/CodeSystem-edqm-standardterms.xlsx
+++ b/ig/ch-term/CodeSystem-edqm-standardterms.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1624" uniqueCount="1095">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1627" uniqueCount="1097">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-15T10:47:47+00:00</t>
+    <t>2023-01-25T14:36:51+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3187,6 +3187,12 @@
   </si>
   <si>
     <t>Intraputaminal use</t>
+  </si>
+  <si>
+    <t>20088000</t>
+  </si>
+  <si>
+    <t>Perilesional use</t>
   </si>
   <si>
     <t>0004</t>
@@ -3615,7 +3621,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D528"/>
+  <dimension ref="A1:D529"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -9952,9 +9958,21 @@
         <v>1094</v>
       </c>
       <c r="C528" t="s" s="2">
+        <v>1095</v>
+      </c>
+      <c r="D528" s="2"/>
+    </row>
+    <row r="529">
+      <c r="A529" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B529" t="s" s="2">
+        <v>1096</v>
+      </c>
+      <c r="C529" t="s" s="2">
         <v>927</v>
       </c>
-      <c r="D528" s="2"/>
+      <c r="D529" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
